--- a/Result/profitability/8341.xlsx
+++ b/Result/profitability/8341.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03625</v>
+        <v>1.06875</v>
       </c>
       <c r="N2" t="n">
-        <v>44.50875</v>
+        <v>44.585</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9087499999999999</v>
+        <v>0.9662500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>44.13375</v>
+        <v>44.0175</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8025</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>43.76</v>
+        <v>43.885</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6837500000000001</v>
+        <v>0.7512500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>43.6475</v>
+        <v>43.95625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6925000000000001</v>
+        <v>0.7037500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>43.7075</v>
+        <v>43.73125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>0.49625</v>
+        <v>0.57</v>
       </c>
       <c r="N7" t="n">
-        <v>43.50875</v>
+        <v>43.96125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8429,6 +8429,133 @@
       </c>
       <c r="AM63" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>8341</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D64" t="n">
+        <v>615</v>
+      </c>
+      <c r="E64" t="n">
+        <v>503</v>
+      </c>
+      <c r="F64" t="n">
+        <v>45</v>
+      </c>
+      <c r="G64" t="n">
+        <v>314</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>28.07%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>317</v>
+      </c>
+      <c r="K64" t="n">
+        <v>191</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N64" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-0.02649006622516559</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.08759124087591241</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.5399999999999999</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.5806451612903225</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.469999999999999</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.05807665177521737</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
